--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T06:34:41+00:00</t>
+    <t>2024-04-11T09:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-11T09:53:59+00:00</t>
+    <t>2024-04-12T06:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T06:23:14+00:00</t>
+    <t>2024-04-16T10:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-16T10:58:26+00:00</t>
+    <t>2024-04-18T15:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:20:26+00:00</t>
+    <t>2024-04-18T15:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="68">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:27:51+00:00</t>
+    <t>2024-04-22T11:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -106,12 +106,48 @@
     <t>child</t>
   </si>
   <si>
+    <t>DAUC</t>
+  </si>
+  <si>
+    <t>daughter</t>
+  </si>
+  <si>
+    <t>SONC</t>
+  </si>
+  <si>
+    <t>son</t>
+  </si>
+  <si>
+    <t>GRNDCHILD</t>
+  </si>
+  <si>
+    <t>grandchild</t>
+  </si>
+  <si>
+    <t>CHLDINLAW</t>
+  </si>
+  <si>
+    <t>child-in-law</t>
+  </si>
+  <si>
     <t>PRN</t>
   </si>
   <si>
     <t>parent</t>
   </si>
   <si>
+    <t>FTH</t>
+  </si>
+  <si>
+    <t>father</t>
+  </si>
+  <si>
+    <t>MTH</t>
+  </si>
+  <si>
+    <t>mother</t>
+  </si>
+  <si>
     <t>SIB</t>
   </si>
   <si>
@@ -157,7 +193,7 @@
     <t>NOK</t>
   </si>
   <si>
-    <t>next-of-kin</t>
+    <t>next of kin</t>
   </si>
   <si>
     <t>POWATT</t>
@@ -445,7 +481,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -553,15 +589,63 @@
         <v>50</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -580,28 +664,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T11:01:11+00:00</t>
+    <t>2024-04-22T12:03:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="70">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T12:03:36+00:00</t>
+    <t>2024-04-22T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -98,6 +98,12 @@
   </si>
   <si>
     <t>Concept</t>
+  </si>
+  <si>
+    <t>FAMMEMB</t>
+  </si>
+  <si>
+    <t>family member</t>
   </si>
   <si>
     <t>CHILD</t>
@@ -481,7 +487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -637,15 +643,23 @@
         <v>62</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>64</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -664,28 +678,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T13:38:01+00:00</t>
+    <t>2024-04-23T08:24:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T08:24:27+00:00</t>
+    <t>2024-04-23T10:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T10:50:14+00:00</t>
+    <t>2024-04-23T18:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T18:15:55+00:00</t>
+    <t>2024-05-02T12:47:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -103,109 +103,55 @@
     <t>FAMMEMB</t>
   </si>
   <si>
-    <t>family member</t>
-  </si>
-  <si>
     <t>CHILD</t>
   </si>
   <si>
-    <t>child</t>
-  </si>
-  <si>
     <t>DAUC</t>
   </si>
   <si>
-    <t>daughter</t>
-  </si>
-  <si>
     <t>SONC</t>
   </si>
   <si>
-    <t>son</t>
-  </si>
-  <si>
     <t>GRNDCHILD</t>
   </si>
   <si>
-    <t>grandchild</t>
-  </si>
-  <si>
     <t>CHLDINLAW</t>
   </si>
   <si>
-    <t>child-in-law</t>
-  </si>
-  <si>
     <t>PRN</t>
   </si>
   <si>
-    <t>parent</t>
-  </si>
-  <si>
     <t>FTH</t>
   </si>
   <si>
-    <t>father</t>
-  </si>
-  <si>
     <t>MTH</t>
   </si>
   <si>
-    <t>mother</t>
-  </si>
-  <si>
     <t>SIB</t>
   </si>
   <si>
-    <t>sibling</t>
-  </si>
-  <si>
     <t>DOMPART</t>
   </si>
   <si>
-    <t>domestic partner</t>
-  </si>
-  <si>
     <t>SPS</t>
   </si>
   <si>
-    <t>spouse</t>
-  </si>
-  <si>
     <t>FRND</t>
   </si>
   <si>
-    <t>unrelated friend</t>
-  </si>
-  <si>
     <t>NBOR</t>
   </si>
   <si>
-    <t>neighbor</t>
-  </si>
-  <si>
     <t>ROOM</t>
   </si>
   <si>
-    <t>Roommate</t>
-  </si>
-  <si>
     <t>GUARD</t>
   </si>
   <si>
-    <t>guardian</t>
-  </si>
-  <si>
     <t>NOK</t>
   </si>
   <si>
-    <t>next of kin</t>
-  </si>
-  <si>
     <t>POWATT</t>
-  </si>
-  <si>
-    <t>power of attorney</t>
   </si>
   <si>
     <t/>
@@ -506,160 +452,124 @@
       <c r="A2" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>29</v>
-      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>37</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>39</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>41</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>43</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>45</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>47</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>49</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>51</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>53</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>55</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>57</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>59</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>61</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>63</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>64</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -678,28 +588,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>67</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>68</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>64</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>69</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T12:47:39+00:00</t>
+    <t>2024-05-03T13:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T13:03:24+00:00</t>
+    <t>2024-05-06T06:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T06:35:09+00:00</t>
+    <t>2024-05-06T07:49:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T07:49:19+00:00</t>
+    <t>2024-05-06T14:14:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T14:14:33+00:00</t>
+    <t>2024-05-10T08:40:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T08:40:47+00:00</t>
+    <t>2024-05-10T19:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T19:12:38+00:00</t>
+    <t>2024-05-12T08:40:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:40:34+00:00</t>
+    <t>2024-05-12T08:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:41:58+00:00</t>
+    <t>2024-05-12T09:45:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T09:45:49+00:00</t>
+    <t>2024-05-12T11:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T11:37:02+00:00</t>
+    <t>2024-06-03T20:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T20:51:53+00:00</t>
+    <t>2024-06-25T21:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:42:34+00:00</t>
+    <t>2024-06-26T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -7,14 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from RoleCode" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from DK Related Perso" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="53">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -152,6 +152,9 @@
   </si>
   <si>
     <t>POWATT</t>
+  </si>
+  <si>
+    <t>ECON</t>
   </si>
   <si>
     <t/>
@@ -433,7 +436,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -560,16 +563,22 @@
       <c r="A20" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="B20" t="s" s="2">
-        <v>46</v>
-      </c>
+      <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
         <v>47</v>
       </c>
       <c r="B21" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
         <v>48</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -588,28 +597,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:12:58+00:00</t>
+    <t>2024-10-17T12:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:15:17+00:00</t>
+    <t>2024-10-18T06:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.4.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T12:45:46+00:00</t>
+    <t>2024-11-15T12:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T12:49:28+00:00</t>
+    <t>2024-11-15T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T13:03:47+00:00</t>
+    <t>2024-11-29T07:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T07:41:39+00:00</t>
+    <t>2024-11-29T10:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T10:20:07+00:00</t>
+    <t>2024-12-11T08:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T08:38:49+00:00</t>
+    <t>2024-12-11T09:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T09:50:58+00:00</t>
+    <t>2024-12-16T15:09:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:09:03+00:00</t>
+    <t>2024-12-16T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
+++ b/ValueSet-dk-core-RelatedPersonRelationshipTypes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:16:17+00:00</t>
+    <t>2024-12-16T15:31:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
